--- a/signup_forms/023_membership_club_join_form--signup_forms.xlsx
+++ b/signup_forms/023_membership_club_join_form--signup_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -919,12 +919,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>zip_code</t>
+          <t>zip_code_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zip Code</t>
+          <t>Zip Code 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -942,12 +942,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>country_of_residence</t>
+          <t>country_of_residence_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Country of Residence</t>
+          <t>Country Of Residence 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -965,12 +965,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>state_of_residence</t>
+          <t>state_of_residence_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>State of Residence</t>
+          <t>State Of Residence 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -988,12 +988,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>city_of_residence</t>
+          <t>city_of_residence_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>City of Residence</t>
+          <t>City Of Residence 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1314,7 +1314,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>country_of_residence_choices</t>
+          <t>country_of_residence_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>country_of_residence_choices</t>
+          <t>country_of_residence_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1348,7 +1348,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>state_of_residence_choices</t>
+          <t>state_of_residence_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1365,7 +1365,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>state_of_residence_choices</t>
+          <t>state_of_residence_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>city_of_residence_choices</t>
+          <t>city_of_residence_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>city_of_residence_choices</t>
+          <t>city_of_residence_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
